--- a/runs/KO/2026-10-13/bear/scratch/gen_wo_irs/dcf.xlsx
+++ b/runs/KO/2026-10-13/bear/scratch/gen_wo_irs/dcf.xlsx
@@ -972,7 +972,7 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>0.03</v>
@@ -1018,7 +1018,7 @@
         <v/>
       </c>
       <c r="I3" s="4" t="n">
-        <v>52862.02214222582</v>
+        <v>52363.32382012936</v>
       </c>
     </row>
     <row r="4">
@@ -1075,7 +1075,7 @@
         <v/>
       </c>
       <c r="I5" s="4" t="n">
-        <v>17545.43376922617</v>
+        <v>17379.91080913914</v>
       </c>
     </row>
     <row r="6">
@@ -1240,7 +1240,7 @@
         <v/>
       </c>
       <c r="I11" s="4" t="n">
-        <v>12634.26193579465</v>
+        <v>12515.07078545696</v>
       </c>
     </row>
     <row r="12">
@@ -1351,7 +1351,7 @@
         <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>9509.197791601118</v>
+        <v>9419.488378472806</v>
       </c>
     </row>
     <row r="16">
@@ -1419,7 +1419,7 @@
         <v/>
       </c>
       <c r="C20" s="4" t="n">
-        <v>51035.10648310421</v>
+        <v>50512.10485134534</v>
       </c>
     </row>
     <row r="21">
@@ -1433,7 +1433,7 @@
         <v/>
       </c>
       <c r="C21" s="4" t="n">
-        <v>12471.38149156303</v>
+        <v>12353.7269491898</v>
       </c>
     </row>
     <row r="22">
@@ -1447,7 +1447,7 @@
         <v/>
       </c>
       <c r="C22" s="4" t="n">
-        <v>354488.4111845487</v>
+        <v>351144.1808903549</v>
       </c>
     </row>
     <row r="23">
@@ -1461,7 +1461,7 @@
         <v/>
       </c>
       <c r="C23" s="4" t="n">
-        <v>266806.2791411711</v>
+        <v>264289.2387719148</v>
       </c>
     </row>
     <row r="24">
@@ -1475,7 +1475,7 @@
         <v/>
       </c>
       <c r="C24" s="4" t="n">
-        <v>317841.3856242754</v>
+        <v>314801.3436232602</v>
       </c>
     </row>
     <row r="25">
@@ -1503,7 +1503,7 @@
         <v/>
       </c>
       <c r="C26" s="4" t="n">
-        <v>318252.8856242754</v>
+        <v>315212.8436232602</v>
       </c>
     </row>
     <row r="27">
@@ -1517,7 +1517,7 @@
         <v/>
       </c>
       <c r="C27" s="4" t="n">
-        <v>325880.9849622021</v>
+        <v>322683.1312451401</v>
       </c>
     </row>
     <row r="28">
@@ -1531,7 +1531,7 @@
         <v/>
       </c>
       <c r="C28" s="4" t="n">
-        <v>75.75104252956812</v>
+        <v>75.00770135870296</v>
       </c>
     </row>
     <row r="29">
@@ -1545,7 +1545,7 @@
         <v/>
       </c>
       <c r="C29" s="6" t="n">
-        <v>-0.1594425186</v>
+        <v>-0.1676908669</v>
       </c>
     </row>
   </sheetData>
